--- a/seguimiento/matrices/Matriz de comandos por impacto.xlsx
+++ b/seguimiento/matrices/Matriz de comandos por impacto.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Comunicarse sin repetir la configuracion de idioma</t>
+          <t>Empezar a conversar en menos de un minuto</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Comunicarse sin repetir la configuracion de idioma</t>
+          <t>Empezar a conversar en menos de un minuto</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Conversar de forma continua</t>
+          <t>Mantener el contexto de toda la charla</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -981,19 +981,19 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Reporte (pendiente: no existe entidad)</t>
+          <t>Reporte (tabla de soporte, ADR-008)</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Participar en la conversacion en el propio idioma</t>
+          <t>Participar en su idioma sin instalar la app ni crear cuenta</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Participar en la conversacion en el propio idioma</t>
+          <t>Participar en su idioma sin instalar la app ni crear cuenta</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Gestionar la configuracion de idiomas y regiones</t>
+          <t>Ampliar la oferta de idiomas y regiones con calidad</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Reporte (pendiente: no existe entidad)</t>
+          <t>Reporte (tabla de soporte, ADR-008)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1169,6 +1169,70 @@
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Acceder a la cuenta de forma segura</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Eliminar mi cuenta</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Comando</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Cliente Traductor</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Usuario, Conversacion, MensajeOriginal, MensajeDestino, Reporte</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Ley 1581 (derecho al olvido)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Acceder a la cuenta de forma segura</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Renovar la sesion</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Comando</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Cliente Traductor</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Token de refresco (soporte)</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Usuario-RN-10</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1204,7 +1268,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Hay dos filas con 'Reporte (pendiente)': el reporte de mala traduccion aparece como responsabilidad de Lenguaje, pero no existe una entidad Reporte. Hay que decidir si se crea al cerrar el modelo de dominio.</t>
+          <t>Reporte es una tabla de soporte, no un objeto de dominio (el mentor dijo que los reportes son dinamicos); ver ADR-008.</t>
         </is>
       </c>
     </row>
